--- a/GAIA_Assessment_Tool.xlsx
+++ b/GAIA_Assessment_Tool.xlsx
@@ -18,7 +18,8 @@
     <sheet name="Usage Log" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Methodology &amp; Sources" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Framework Comparison" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Changelog" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SDG &amp; Reporting Map" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Changelog" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -804,7 +805,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Version 2.0.0 · 2026-07-06 · MIT License · Generated by build_workbook.py from data/*.csv — never hand-edited (FRAMEWORK.md §9)</t>
+          <t>Version 2.1.0 · 2026-07-06 · MIT License · Generated by build_workbook.py from data/*.csv — never hand-edited (FRAMEWORK.md §9)</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1570,8 +1571,52 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>ISO/IEC TR 20226:2025</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Standard (technical report)</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Overview of environmental sustainability aspects and metrics of AI systems across their lifecycle (published July 2025)</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>GAIA is an executable companion: it implements the TR's metric categories (energy, water, carbon, embodied) in runnable form; conformance crosswalk on the roadmap (COMPARISON.md §4)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>ITU-T L.1801 (02/2026)</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Standard (ITU-T Recommendation)</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Guidelines for assessing the environmental impact of AI systems</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Same relation: L.1801 gives the assessment guidelines, GAIA the no-code instrument that executes them; tracked each revision cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>What none of these provides — and GAIA does — is the combination of: (a) uncertainty-tiered estimates usable WITHOUT provider cooperation, (b) water alongside carbon, (c) task-conditioned grading of deployments, (d) an explicit frugality check, and (e) an Excel artifact a non-programmer can run. (FRAMEWORK.md §7)</t>
         </is>
@@ -1579,7 +1624,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1591,7 +1636,609 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>What it asks</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>GAIA output that populates it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 6 — Clean water and sanitation</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Target 6.4</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>Substantially increase water-use efficiency across all sectors</t>
+        </is>
+      </c>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Water intensity per functional unit (L/request, L/1M tokens) from the two-path model; trend across periods in the Usage Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 7 — Affordable and clean energy</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Target 7.3</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Double the global rate of improvement in energy efficiency</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>The A–E grade is an energy-intensity rating per task class; Module A' intensity-reduction targets track 7.3 directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 7 — Affordable and clean energy</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Target 7.2</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Increase the share of renewable energy</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Market-based CI input and the low-carbon-region lever document the renewable share of AI electricity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 8 — Decent work and economic growth</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Target 8.4</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Improve resource efficiency; decouple growth from environmental degradation</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Rates-before-totals (P4): footprint per task outcome (R4) is a decoupling metric — AI output vs. resources consumed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 9 — Industry innovation and infrastructure</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Target 9.4</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Upgrade infrastructure for sustainability and resource-use efficiency</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Mitigation levers 1, 2, 8 (right-sizing, reasoning budgets, newer accelerators) with measured effect sizes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 12 — Responsible consumption and production</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Target 12.2</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Sustainable management and efficient use of natural resources</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>The full Ground→Assess inventory: an auditable account of energy and water consumed by AI use</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 12 — Responsible consumption and production</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Target 12.6</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Encourage companies to integrate sustainability information into reporting</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>The GAIA disclosure template (FRAMEWORK.md §8), designed to feed GRI/ESRS/IFRS reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>UN SDG 13 — Climate action</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Targets 13.2 / 13.3</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Integrate climate measures into policies and planning; improve capacity</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Dual-reported carbon totals and intensities; evidence-ranked reduction plan; SCI/GHGP restatement</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>GRI 302-1</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Energy consumption within the organization</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Monthly kWh of self-hosted AI (E_month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>GRI 302-2</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Energy consumption outside the organization</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Monthly kWh of API/cloud AI use</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>GRI 302-3</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Energy intensity</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Wh per functional unit (R1–R4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>GRI 302-4</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Reduction of energy consumption</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Before/after intensity from the mitigation plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>GRI 303-5</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Water consumption</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>On-site path (E_IT × WUE) for owned facilities; two-path total as value-chain context</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>GRI 305-2</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Energy indirect (Scope 2) GHG emissions</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Location- AND market-based carbon of self-hosted deployments, reported separately as GRI requires</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>GRI 305-3</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Other indirect (Scope 3) GHG emissions</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>API-use carbon (categories 1/11 logic per arXiv:2606.10660) plus the embodied adder</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>GRI Standards</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>GRI 305-4</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>GHG emissions intensity</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>kg CO2e per functional unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>ESRS (CSRD)</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>E1-5</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Energy consumption and mix</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>E_month split by deployment path; market CI documents the mix claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>ESRS (CSRD)</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>E1-6</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Gross Scopes 1–3 GHG emissions</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Both Scope-2 methods required by ESRS are native to GAIA (P6 dual reporting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>ESRS (CSRD)</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>E1-4</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Targets related to climate change</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Intensity-reduction targets from Module A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>ESRS (CSRD)</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>E3-4</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Water consumption</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Two-path water total with the on-site/off-site split</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>IFRS S2 (ISSB)</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Cross-industry metrics</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Scopes 1–3, entity-specific metrics</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>GAIA totals as the AI contribution to Scope 2/3; per-FU intensities as entity-specific metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>CDP</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Climate &amp; water questionnaires</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Quantitative fields + methodology disclosure</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Carbon and water modules populate the fields; the data-quality statement answers methodology questions honestly</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>SBTi</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Near-term Scope 2/3 targets</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Validated absolute or intensity trajectories</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>GAIA supplies the AI-use baseline and tracks intensity; totals feed target-setting (grades are not targets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>EU AI Act</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Art. 40/51, Annex XI</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>GPAI energy documentation</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Disclosure-template provider fields accept Annex XI data as it becomes available</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>UN Global Compact</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Principles 7–9</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Precaution, environmental responsibility, clean technology</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>The GAIA report evidences Principle 7 (precautionary quantification) and 9 (diffusion of efficient technology via the lever catalogue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Boundary: GAIA measures the environmental COST of AI use; whether an AI application advances an SDG ('AI for Good') is out of scope — the same boundary ISO/IEC TR 20226:2025 draws. SDG claims in a conforming report must trace to the outputs listed here (P1: traceable or absent). Full capability matrix and gap analysis: COMPARISON.md in the repository.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A28:D28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1619,22 +2266,39 @@
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
+          <t>2.1.0</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr">
+        <is>
+          <t>GAIA 2.1 — comparability release. New 'SDG &amp; Reporting Map' sheet maps GAIA outputs onto UN SDG targets (6.4, 7.2/7.3, 8.4, 9.4, 12.2/12.6, 13.2/13.3), GRI 302/303/305, ESRS E1/E3, IFRS S2, CDP, SBTi, EU AI Act Annex XI, and UN Global Compact Principles 7–9. Framework Comparison extended with ISO/IEC TR 20226:2025 and ITU-T L.1801 (02/2026). Full capability matrix and gap-analysis roadmap: COMPARISON.md. Methodology unchanged (minor version per §9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
           <t>2.0.0</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>GAIA 2.0 — full science-based rebuild. The v1 composite Environmental Score (dimensionally incoherent), Benefit Score (subjective weights) and 'Prohibited' decision matrix are REMOVED; replaced by task-conditioned A–E energy grades on fixed logarithmic bands, a frugality flag (F0/F1/F2+) reported beside the grade, and grade×flag guidance. Per-model water/carbon columns abolished (P3): the model database stores energy only, with source, vintage, tier and bounds; carbon and water are computed from separate sourced Region/Facility tables. Every result is low/central/high (P2); dual location/market carbon reporting (P6); embodied adder (§4.6); two-path water model (§4.4). The workbook is now GENERATED by build_workbook.py from data/*.csv — never hand-edited (§9). Full component-by-component audit of what was kept, rebuilt, and removed: see DECISIONS.md in the repository.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="C4" s="12" t="inlineStr">
+    <row r="5">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Versioning is semantic (§9): factor-table refreshes bump the minor version; methodology changes bump the major version and require a documented rationale against P1–P7. Errors are fixed in the data tables with a changelog entry, never silently.</t>
         </is>
